--- a/jogos_2024-12-17.xlsx
+++ b/jogos_2024-12-17.xlsx
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
         <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.33</v>
+        <v>1.62</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>1.8</v>
+        <v>6.25</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="P7" t="n">
         <v>1.95</v>
       </c>
       <c r="Q7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y7" t="n">
         <v>2.5</v>
       </c>
-      <c r="R7" t="n">
+      <c r="Z7" t="n">
         <v>1.5</v>
       </c>
-      <c r="S7" t="n">
+      <c r="AA7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC7" t="n">
         <v>2.5</v>
       </c>
-      <c r="T7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AD7" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
+          <t>['49', '52', '57']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['42', '45']</t>
-        </is>
-      </c>
       <c r="AG7" t="n">
-        <v>1.77</v>
+        <v>1.09</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.25</v>
+        <v>2.32</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.57</v>
+        <v>4</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45643.52083333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.62</v>
+        <v>4.33</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>6.25</v>
+        <v>1.8</v>
       </c>
       <c r="O8" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
         <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z8" t="n">
         <v>1.53</v>
       </c>
-      <c r="S8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AA8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['49', '52', '57']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['42', '45']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.09</v>
+        <v>1.77</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.32</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="AJ8" t="n">
-        <v>4</v>
+        <v>1.57</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45643.52083333334</v>
@@ -1933,109 +1933,109 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O12" t="n">
         <v>3</v>
       </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M12" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="N12" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2</v>
-      </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>3.35</v>
       </c>
       <c r="R12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U12" t="n">
         <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W12" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X12" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['14', '27', '35', '73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['12']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.06</v>
+        <v>1.42</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.65</v>
+        <v>1.53</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45643.625</v>
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.45</v>
+        <v>1.46</v>
       </c>
       <c r="M13" t="n">
-        <v>3.34</v>
+        <v>4.27</v>
       </c>
       <c r="N13" t="n">
-        <v>2.83</v>
+        <v>6.59</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
         <v>1.4</v>
       </c>
       <c r="V13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['14', '27', '35', '73']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
         <v>1.06</v>
       </c>
-      <c r="W13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
+      <c r="AH13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AI13" t="n">
         <v>1.42</v>
       </c>
-      <c r="AH13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45643.625</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.96</v>
+        <v>4.81</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="N14" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="O14" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="X14" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AC14" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2280,20 +2280,20 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['35', '56', '67']</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45643.69791666666</v>
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.81</v>
+        <v>3.12</v>
       </c>
       <c r="M15" t="n">
-        <v>4.33</v>
+        <v>3.51</v>
       </c>
       <c r="N15" t="n">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD15" t="n">
         <v>2</v>
       </c>
-      <c r="R15" t="n">
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['43', '62', '72']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.33</v>
       </c>
-      <c r="S15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X15" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>['53']</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AI15" t="n">
-        <v>3.22</v>
+        <v>2.26</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45643.69791666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
         <v>3</v>
       </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.12</v>
+        <v>4.96</v>
       </c>
       <c r="M16" t="n">
-        <v>3.51</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>2.12</v>
+        <v>1.65</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="P16" t="n">
         <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T16" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X16" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['35', '56', '67']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
         <v>2</v>
       </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['43', '62', '72']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['19']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.26</v>
+        <v>2.88</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45643.69791666666</v>
